--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136548663</v>
       </c>
       <c r="B3" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548742</v>
       </c>
       <c r="B4" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136548751</v>
       </c>
       <c r="B5" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136548792</v>
       </c>
       <c r="B6" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136550497</v>
       </c>
       <c r="B7" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136538248</v>
       </c>
       <c r="B8" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136538299</v>
       </c>
       <c r="B9" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136548770</v>
       </c>
       <c r="B10" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136550096</v>
       </c>
       <c r="B11" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136550093</v>
       </c>
       <c r="B12" t="n">
-        <v>108437</v>
+        <v>108440</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136548663</v>
       </c>
       <c r="B3" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548742</v>
       </c>
       <c r="B4" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136548751</v>
       </c>
       <c r="B5" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136548792</v>
       </c>
       <c r="B6" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136550497</v>
       </c>
       <c r="B7" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136538248</v>
       </c>
       <c r="B8" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136538299</v>
       </c>
       <c r="B9" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136548770</v>
       </c>
       <c r="B10" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136550096</v>
       </c>
       <c r="B11" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136550093</v>
       </c>
       <c r="B12" t="n">
-        <v>108440</v>
+        <v>108441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136544388</v>
       </c>
       <c r="B2" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136548663</v>
       </c>
       <c r="B3" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548742</v>
       </c>
       <c r="B4" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136548751</v>
       </c>
       <c r="B5" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136548792</v>
       </c>
       <c r="B6" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136550497</v>
       </c>
       <c r="B7" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136538248</v>
       </c>
       <c r="B8" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1425,7 +1425,7 @@
         <v>136538299</v>
       </c>
       <c r="B9" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136548770</v>
       </c>
       <c r="B10" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136550096</v>
       </c>
       <c r="B11" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136550093</v>
       </c>
       <c r="B12" t="n">
-        <v>108441</v>
+        <v>108446</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136548663</v>
       </c>
       <c r="B3" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548742</v>
       </c>
       <c r="B4" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136548751</v>
       </c>
       <c r="B5" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136548792</v>
       </c>
       <c r="B6" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136550497</v>
       </c>
       <c r="B7" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136538248</v>
       </c>
       <c r="B8" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136538299</v>
       </c>
       <c r="B9" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136548770</v>
       </c>
       <c r="B10" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136550096</v>
       </c>
       <c r="B11" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136550093</v>
       </c>
       <c r="B12" t="n">
-        <v>108446</v>
+        <v>108448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136538248</v>
+        <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>108378</v>
+        <v>99270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,34 +1327,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220083</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Z691 Hotagen, Jmt</t>
+          <t>Rötviken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454694</v>
+        <v>454622</v>
       </c>
       <c r="R8" t="n">
-        <v>7093370</v>
+        <v>7093360</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1381,12 +1389,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1395,18 +1403,19 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1416,16 +1425,16 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136538248</t>
+          <t>https://artportalen.se/Sighting/136953907</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136538299</v>
+        <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>108378</v>
+        <v>99270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,34 +1442,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220083</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Z691 Hotagen, Jmt</t>
+          <t>Rötviken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454682</v>
+        <v>454723</v>
       </c>
       <c r="R9" t="n">
-        <v>7093369</v>
+        <v>7093380</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1487,12 +1500,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1507,12 +1520,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1522,13 +1535,13 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136538299</t>
+          <t>https://artportalen.se/Sighting/136953908</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136548770</v>
+        <v>136538248</v>
       </c>
       <c r="B10" t="n">
         <v>108378</v>
@@ -1563,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454636</v>
+        <v>454694</v>
       </c>
       <c r="R10" t="n">
-        <v>7093366</v>
+        <v>7093370</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1628,13 +1641,13 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136548770</t>
+          <t>https://artportalen.se/Sighting/136538248</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136550096</v>
+        <v>136538299</v>
       </c>
       <c r="B11" t="n">
         <v>108378</v>
@@ -1669,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454633</v>
+        <v>454682</v>
       </c>
       <c r="R11" t="n">
-        <v>7093371</v>
+        <v>7093369</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1734,16 +1747,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136550096</t>
+          <t>https://artportalen.se/Sighting/136538299</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136550093</v>
+        <v>136548770</v>
       </c>
       <c r="B12" t="n">
-        <v>108448</v>
+        <v>108378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,21 +1764,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454639</v>
+        <v>454636</v>
       </c>
       <c r="R12" t="n">
-        <v>7093372</v>
+        <v>7093366</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1839,6 +1852,218 @@
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136548770</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136550096</v>
+      </c>
+      <c r="B13" t="n">
+        <v>108378</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Z691 Hotagen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>454633</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7093371</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136550096</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136550093</v>
+      </c>
+      <c r="B14" t="n">
+        <v>108448</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Z691 Hotagen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>454639</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7093372</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136550093</t>
         </is>
@@ -1857,6 +2082,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136548663</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548742</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1001,7 +1001,7 @@
         <v>136548751</v>
       </c>
       <c r="B5" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136548792</v>
       </c>
       <c r="B6" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136550497</v>
       </c>
       <c r="B7" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>136538248</v>
       </c>
       <c r="B10" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136538299</v>
       </c>
       <c r="B11" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136548770</v>
       </c>
       <c r="B12" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>136550096</v>
       </c>
       <c r="B13" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>136550093</v>
       </c>
       <c r="B14" t="n">
-        <v>108448</v>
+        <v>108454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136548663</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548742</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1001,7 +1001,7 @@
         <v>136548751</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136548792</v>
       </c>
       <c r="B6" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136550497</v>
       </c>
       <c r="B7" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>136538248</v>
       </c>
       <c r="B10" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136538299</v>
       </c>
       <c r="B11" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136548770</v>
       </c>
       <c r="B12" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>136550096</v>
       </c>
       <c r="B13" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>136550093</v>
       </c>
       <c r="B14" t="n">
-        <v>108454</v>
+        <v>108456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>136548663</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -895,7 +895,7 @@
         <v>136548742</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136548751</v>
       </c>
       <c r="B5" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136548792</v>
       </c>
       <c r="B6" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136550497</v>
       </c>
       <c r="B7" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>136538248</v>
       </c>
       <c r="B10" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136538299</v>
       </c>
       <c r="B11" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136548770</v>
       </c>
       <c r="B12" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>136550096</v>
       </c>
       <c r="B13" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1968,7 +1968,7 @@
         <v>136550093</v>
       </c>
       <c r="B14" t="n">
-        <v>108456</v>
+        <v>108457</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136548663</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548742</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136548751</v>
       </c>
       <c r="B5" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136548792</v>
       </c>
       <c r="B6" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136550497</v>
       </c>
       <c r="B7" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>136538248</v>
       </c>
       <c r="B10" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136538299</v>
       </c>
       <c r="B11" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136548770</v>
       </c>
       <c r="B12" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>136550096</v>
       </c>
       <c r="B13" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>136550093</v>
       </c>
       <c r="B14" t="n">
-        <v>108457</v>
+        <v>108463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136548663</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548742</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136548751</v>
       </c>
       <c r="B5" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136548792</v>
       </c>
       <c r="B6" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136550497</v>
       </c>
       <c r="B7" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>136538248</v>
       </c>
       <c r="B10" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136538299</v>
       </c>
       <c r="B11" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136548770</v>
       </c>
       <c r="B12" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>136550096</v>
       </c>
       <c r="B13" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>136550093</v>
       </c>
       <c r="B14" t="n">
-        <v>108463</v>
+        <v>108467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136548663</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548742</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136548751</v>
       </c>
       <c r="B5" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136548792</v>
       </c>
       <c r="B6" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136550497</v>
       </c>
       <c r="B7" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>136538248</v>
       </c>
       <c r="B10" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136538299</v>
       </c>
       <c r="B11" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136548770</v>
       </c>
       <c r="B12" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>136550096</v>
       </c>
       <c r="B13" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>136550093</v>
       </c>
       <c r="B14" t="n">
-        <v>108467</v>
+        <v>108469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136548663</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548742</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1001,7 +1001,7 @@
         <v>136548751</v>
       </c>
       <c r="B5" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1107,7 +1107,7 @@
         <v>136548792</v>
       </c>
       <c r="B6" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136550497</v>
       </c>
       <c r="B7" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>136538248</v>
       </c>
       <c r="B10" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136538299</v>
       </c>
       <c r="B11" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136548770</v>
       </c>
       <c r="B12" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1862,7 +1862,7 @@
         <v>136550096</v>
       </c>
       <c r="B13" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>136550093</v>
       </c>
       <c r="B14" t="n">
-        <v>108469</v>
+        <v>108471</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136544388</v>
       </c>
       <c r="B2" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136548663</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548742</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1001,7 +1001,7 @@
         <v>136548751</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1107,7 +1107,7 @@
         <v>136548792</v>
       </c>
       <c r="B6" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136550497</v>
       </c>
       <c r="B7" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>136538248</v>
       </c>
       <c r="B10" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1650,7 +1650,7 @@
         <v>136538299</v>
       </c>
       <c r="B11" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136548770</v>
       </c>
       <c r="B12" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1862,7 +1862,7 @@
         <v>136550096</v>
       </c>
       <c r="B13" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>136550093</v>
       </c>
       <c r="B14" t="n">
-        <v>108471</v>
+        <v>108484</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136544388</v>
       </c>
       <c r="B2" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136548663</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136548742</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136548751</v>
       </c>
       <c r="B5" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136548792</v>
       </c>
       <c r="B6" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136550497</v>
       </c>
       <c r="B7" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>136538248</v>
       </c>
       <c r="B10" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1650,7 +1650,7 @@
         <v>136538299</v>
       </c>
       <c r="B11" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>136548770</v>
       </c>
       <c r="B12" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>136550096</v>
       </c>
       <c r="B13" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>136550093</v>
       </c>
       <c r="B14" t="n">
-        <v>108484</v>
+        <v>108486</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26805-2023 artfynd.xlsx
+++ b/artfynd/A 26805-2023 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136953907</v>
       </c>
       <c r="B8" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136953908</v>
       </c>
       <c r="B9" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
